--- a/03_Outputs/Agroindustrial_Occidente/01_Generalidades/distribucion_territorial.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/01_Generalidades/distribucion_territorial.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -32,23 +32,56 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -68,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -77,6 +110,12 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,12 +444,12 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,22 +740,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>area_km2</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>participacion_area_prov_pct</t>
         </is>
@@ -812,29 +852,29 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>ind_mpio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>subregion</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
@@ -972,22 +1012,22 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Área municipal (km²)</t>
         </is>
